--- a/out/08_ISMS/SNX-ISMS-REG-04 User Access Register Periodic Review (Rev00 DRAFT).xlsx
+++ b/out/08_ISMS/SNX-ISMS-REG-04 User Access Register Periodic Review (Rev00 DRAFT).xlsx
@@ -15,8 +15,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Daftar'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Register Akses'!$A$4:$S$256</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Register Akses'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Review Periodik'!$A$4:$L$205</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Review Periodik'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -170,7 +173,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -300,6 +303,33 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -701,8 +731,15 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="24">
-      <c r="A4" s="27" t="inlineStr">
+    <row r="3" s="24">
+      <c r="A3" s="44" t="n"/>
+      <c r="B3" s="44" t="n"/>
+      <c r="C3" s="44" t="n"/>
+      <c r="D3" s="44" t="n"/>
+      <c r="E3" s="44" t="n"/>
+    </row>
+    <row r="4" ht="16.5" customHeight="1" s="24">
+      <c r="A4" s="45" t="inlineStr">
         <is>
           <t>Nomor dokumen</t>
         </is>
@@ -712,9 +749,12 @@
           <t>SNX-ISMS-REG-04</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="24">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="C4" s="44" t="n"/>
+      <c r="D4" s="44" t="n"/>
+      <c r="E4" s="44" t="n"/>
+    </row>
+    <row r="5" ht="16.5" customHeight="1" s="24">
+      <c r="A5" s="45" t="inlineStr">
         <is>
           <t>Judul</t>
         </is>
@@ -724,9 +764,12 @@
           <t>User Access Register &amp; Periodic Access Review</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="24">
-      <c r="A6" s="27" t="inlineStr">
+      <c r="C5" s="44" t="n"/>
+      <c r="D5" s="44" t="n"/>
+      <c r="E5" s="44" t="n"/>
+    </row>
+    <row r="6" ht="16.5" customHeight="1" s="24">
+      <c r="A6" s="45" t="inlineStr">
         <is>
           <t>Revisi</t>
         </is>
@@ -736,9 +779,12 @@
           <t>00 (Draft)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="24">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="C6" s="44" t="n"/>
+      <c r="D6" s="44" t="n"/>
+      <c r="E6" s="44" t="n"/>
+    </row>
+    <row r="7" ht="16.5" customHeight="1" s="24">
+      <c r="A7" s="45" t="inlineStr">
         <is>
           <t>Tanggal draft</t>
         </is>
@@ -748,9 +794,12 @@
           <t>13 Oktober 2026</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="24">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="C7" s="44" t="n"/>
+      <c r="D7" s="44" t="n"/>
+      <c r="E7" s="44" t="n"/>
+    </row>
+    <row r="8" ht="16.5" customHeight="1" s="24">
+      <c r="A8" s="45" t="inlineStr">
         <is>
           <t>Tanggal efektif</t>
         </is>
@@ -760,9 +809,12 @@
           <t>Ditetapkan saat pengesahan</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="24">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="C8" s="44" t="n"/>
+      <c r="D8" s="44" t="n"/>
+      <c r="E8" s="44" t="n"/>
+    </row>
+    <row r="9" ht="16.5" customHeight="1" s="24">
+      <c r="A9" s="45" t="inlineStr">
         <is>
           <t>Klasifikasi</t>
         </is>
@@ -772,9 +824,12 @@
           <t>RESTRICTED (Internal)</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="24">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="C9" s="44" t="n"/>
+      <c r="D9" s="44" t="n"/>
+      <c r="E9" s="44" t="n"/>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="24">
+      <c r="A10" s="45" t="inlineStr">
         <is>
           <t>Pemilik dokumen</t>
         </is>
@@ -784,9 +839,12 @@
           <t>Head of Operation</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="24">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="C10" s="44" t="n"/>
+      <c r="D10" s="44" t="n"/>
+      <c r="E10" s="44" t="n"/>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" s="24">
+      <c r="A11" s="45" t="inlineStr">
         <is>
           <t>Disetujui oleh</t>
         </is>
@@ -796,9 +854,12 @@
           <t>Samuel Kristanto Utomo / President Director</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="24">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="C11" s="44" t="n"/>
+      <c r="D11" s="44" t="n"/>
+      <c r="E11" s="44" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1" s="24">
+      <c r="A12" s="45" t="inlineStr">
         <is>
           <t>Acuan ISO 9001:2015</t>
         </is>
@@ -808,9 +869,12 @@
           <t>Klausul 7.1.3</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="24">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="C12" s="44" t="n"/>
+      <c r="D12" s="44" t="n"/>
+      <c r="E12" s="44" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1" s="24">
+      <c r="A13" s="45" t="inlineStr">
         <is>
           <t>Acuan ISO/IEC 27001:2022</t>
         </is>
@@ -820,9 +884,12 @@
           <t>Kontrol Annex A 5.15, 5.18, 8.2</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="24">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="C13" s="44" t="n"/>
+      <c r="D13" s="44" t="n"/>
+      <c r="E13" s="44" t="n"/>
+    </row>
+    <row r="14" ht="30" customHeight="1" s="24">
+      <c r="A14" s="45" t="inlineStr">
         <is>
           <t>Masa simpan record</t>
         </is>
@@ -832,136 +899,196 @@
           <t>3 tahun</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="23.85" customHeight="1" s="24">
-      <c r="A15" s="27" t="inlineStr">
+      <c r="C14" s="44" t="n"/>
+      <c r="D14" s="44" t="n"/>
+      <c r="E14" s="44" t="n"/>
+    </row>
+    <row r="15" ht="43.5" customHeight="1" s="24">
+      <c r="A15" s="45" t="inlineStr">
         <is>
           <t>Tujuan</t>
         </is>
       </c>
       <c r="B15" s="28" t="inlineStr">
         <is>
-          <t>Register hak akses pengguna ke sistem internal dan sistem pelanggan, serta catatan review akses periodik sesuai SNX-ISMS-SOP-02.</t>
+          <t>Mencatat hak akses pengguna ke sistem internal dan sistem pelanggan, serta hasil review akses periodik sesuai SNX-ISMS-SOP-02.</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="24">
-      <c r="A17" s="29" t="inlineStr">
+      <c r="C15" s="44" t="n"/>
+      <c r="D15" s="44" t="n"/>
+      <c r="E15" s="44" t="n"/>
+    </row>
+    <row r="16" s="24">
+      <c r="A16" s="44" t="n"/>
+      <c r="B16" s="44" t="n"/>
+      <c r="C16" s="44" t="n"/>
+      <c r="D16" s="44" t="n"/>
+      <c r="E16" s="44" t="n"/>
+    </row>
+    <row r="17" ht="16.5" customHeight="1" s="24">
+      <c r="A17" s="46" t="inlineStr">
         <is>
           <t>Cara pakai</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="24">
-      <c r="A18" s="30" t="inlineStr">
+      <c r="B17" s="44" t="n"/>
+      <c r="C17" s="44" t="n"/>
+      <c r="D17" s="44" t="n"/>
+      <c r="E17" s="44" t="n"/>
+    </row>
+    <row r="18" ht="30" customHeight="1" s="24">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
       </c>
       <c r="B18" s="31" t="inlineStr">
         <is>
-          <t>Satu baris per akun per sistem. Jangan pernah menulis password atau token di file ini.</t>
+          <t>Isi satu baris untuk setiap akun di setiap sistem. Jangan menulis password atau token di file ini.</t>
         </is>
       </c>
-    </row>
-    <row r="19" ht="23.85" customHeight="1" s="24">
-      <c r="A19" s="30" t="inlineStr">
+      <c r="C18" s="44" t="n"/>
+      <c r="D18" s="44" t="n"/>
+      <c r="E18" s="44" t="n"/>
+    </row>
+    <row r="19" ht="43.5" customHeight="1" s="24">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
       <c r="B19" s="31" t="inlineStr">
         <is>
-          <t>Kolom Privileged, Review berikutnya, dan Cek dihitung otomatis: privileged ditinjau triwulanan, akses biasa semesteran.</t>
+          <t>Kolom Privileged, Review berikutnya, dan Cek terisi otomatis. Review akses privileged dilakukan setiap triwulan, akses biasa setiap semester.</t>
         </is>
       </c>
-    </row>
-    <row r="20" ht="23.85" customHeight="1" s="24">
-      <c r="A20" s="30" t="inlineStr">
+      <c r="C19" s="44" t="n"/>
+      <c r="D19" s="44" t="n"/>
+      <c r="E19" s="44" t="n"/>
+    </row>
+    <row r="20" ht="43.5" customHeight="1" s="24">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
       </c>
       <c r="B20" s="31" t="inlineStr">
         <is>
-          <t>Cek = CABUT bila personel berstatus Keluar tetapi akun masih Aktif; Cek = KEDALUWARSA bila Berlaku sampai lewat; Cek = REVIEW bila review terlambat.</t>
+          <t>Cek = CABUT jika personel berstatus Keluar tetapi akun masih Aktif; Cek = KEDALUWARSA jika tanggal Berlaku sampai sudah terlampaui; Cek = REVIEW jika review terlambat.</t>
         </is>
       </c>
-    </row>
-    <row r="21" ht="23.85" customHeight="1" s="24">
-      <c r="A21" s="30" t="inlineStr">
+      <c r="C20" s="44" t="n"/>
+      <c r="D20" s="44" t="n"/>
+      <c r="E20" s="44" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1" s="24">
+      <c r="A21" s="31" t="inlineStr">
         <is>
           <t>4.</t>
         </is>
       </c>
       <c r="B21" s="31" t="inlineStr">
         <is>
-          <t>Hasil review periodik dicatat di sheet Review Periodik; tindak lanjut maksimal 10 hari kerja.</t>
+          <t>Catat hasil review periodik di sheet Review Periodik. Selesaikan tindak lanjutnya paling lambat 10 hari kerja.</t>
         </is>
       </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="24">
-      <c r="A23" s="29" t="inlineStr">
+      <c r="C21" s="44" t="n"/>
+      <c r="D21" s="44" t="n"/>
+      <c r="E21" s="44" t="n"/>
+    </row>
+    <row r="22" s="24">
+      <c r="A22" s="44" t="n"/>
+      <c r="B22" s="44" t="n"/>
+      <c r="C22" s="44" t="n"/>
+      <c r="D22" s="44" t="n"/>
+      <c r="E22" s="44" t="n"/>
+    </row>
+    <row r="23" ht="16.5" customHeight="1" s="24">
+      <c r="A23" s="46" t="inlineStr">
         <is>
           <t>Legenda warna</t>
         </is>
       </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="24">
-      <c r="A24" s="32" t="n"/>
-      <c r="B24" s="30" t="inlineStr">
+      <c r="B23" s="44" t="n"/>
+      <c r="C23" s="44" t="n"/>
+      <c r="D23" s="44" t="n"/>
+      <c r="E23" s="44" t="n"/>
+    </row>
+    <row r="24" ht="16.5" customHeight="1" s="24">
+      <c r="A24" s="47" t="n"/>
+      <c r="B24" s="31" t="inlineStr">
         <is>
           <t>Sel input: diisi pengguna</t>
         </is>
       </c>
+      <c r="C24" s="44" t="n"/>
+      <c r="D24" s="44" t="n"/>
+      <c r="E24" s="44" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1" s="24">
-      <c r="A25" s="33" t="n"/>
-      <c r="B25" s="30" t="n"/>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="24">
-      <c r="A26" s="34" t="n"/>
-      <c r="B26" s="30" t="inlineStr">
+      <c r="A25" s="48" t="n"/>
+      <c r="B25" s="31" t="n"/>
+      <c r="C25" s="44" t="n"/>
+      <c r="D25" s="44" t="n"/>
+      <c r="E25" s="44" t="n"/>
+    </row>
+    <row r="26" ht="16.5" customHeight="1" s="24">
+      <c r="A26" s="49" t="n"/>
+      <c r="B26" s="31" t="inlineStr">
         <is>
           <t>Sel rumus: jangan diubah</t>
         </is>
       </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="24">
-      <c r="A28" s="29" t="inlineStr">
+      <c r="C26" s="44" t="n"/>
+      <c r="D26" s="44" t="n"/>
+      <c r="E26" s="44" t="n"/>
+    </row>
+    <row r="27" s="24">
+      <c r="A27" s="44" t="n"/>
+      <c r="B27" s="44" t="n"/>
+      <c r="C27" s="44" t="n"/>
+      <c r="D27" s="44" t="n"/>
+      <c r="E27" s="44" t="n"/>
+    </row>
+    <row r="28" ht="16.5" customHeight="1" s="24">
+      <c r="A28" s="46" t="inlineStr">
         <is>
           <t>Riwayat revisi</t>
         </is>
       </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="24">
-      <c r="A29" s="35" t="inlineStr">
+      <c r="B28" s="44" t="n"/>
+      <c r="C28" s="44" t="n"/>
+      <c r="D28" s="44" t="n"/>
+      <c r="E28" s="44" t="n"/>
+    </row>
+    <row r="29" ht="16.5" customHeight="1" s="24">
+      <c r="A29" s="39" t="inlineStr">
         <is>
           <t>Revisi</t>
         </is>
       </c>
-      <c r="B29" s="35" t="inlineStr">
+      <c r="B29" s="39" t="inlineStr">
         <is>
           <t>Tanggal</t>
         </is>
       </c>
-      <c r="C29" s="35" t="inlineStr">
+      <c r="C29" s="39" t="inlineStr">
         <is>
           <t>Uraian perubahan</t>
         </is>
       </c>
-      <c r="D29" s="35" t="inlineStr">
+      <c r="D29" s="39" t="inlineStr">
         <is>
           <t>Disusun</t>
         </is>
       </c>
-      <c r="E29" s="35" t="inlineStr">
+      <c r="E29" s="39" t="inlineStr">
         <is>
           <t>Disetujui</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="23.85" customHeight="1" s="24">
+    <row r="30" ht="30" customHeight="1" s="24">
       <c r="A30" s="28" t="inlineStr">
         <is>
           <t>00</t>
@@ -995,77 +1122,91 @@
       <c r="D31" s="28" t="n"/>
       <c r="E31" s="28" t="n"/>
     </row>
-    <row r="32"/>
-    <row r="33" ht="15" customHeight="1" s="24">
-      <c r="A33" s="29" t="inlineStr">
+    <row r="32" s="24">
+      <c r="A32" s="44" t="n"/>
+      <c r="B32" s="44" t="n"/>
+      <c r="C32" s="44" t="n"/>
+      <c r="D32" s="44" t="n"/>
+      <c r="E32" s="44" t="n"/>
+    </row>
+    <row r="33" ht="16.5" customHeight="1" s="24">
+      <c r="A33" s="46" t="inlineStr">
         <is>
           <t>Pengesahan</t>
         </is>
       </c>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="24">
-      <c r="A34" s="35" t="inlineStr">
+      <c r="B33" s="44" t="n"/>
+      <c r="C33" s="44" t="n"/>
+      <c r="D33" s="44" t="n"/>
+      <c r="E33" s="44" t="n"/>
+    </row>
+    <row r="34" ht="16.5" customHeight="1" s="24">
+      <c r="A34" s="39" t="inlineStr">
         <is>
           <t>Peran</t>
         </is>
       </c>
-      <c r="B34" s="35" t="inlineStr">
+      <c r="B34" s="39" t="inlineStr">
         <is>
           <t>Nama dan jabatan</t>
         </is>
       </c>
-      <c r="C34" s="35" t="inlineStr">
+      <c r="C34" s="39" t="inlineStr">
         <is>
           <t>Tanda tangan</t>
         </is>
       </c>
-      <c r="D34" s="35" t="inlineStr">
+      <c r="D34" s="39" t="inlineStr">
         <is>
           <t>Tanggal</t>
         </is>
       </c>
+      <c r="E34" s="44" t="n"/>
     </row>
     <row r="35" ht="27.75" customHeight="1" s="24">
-      <c r="A35" s="36" t="inlineStr">
+      <c r="A35" s="28" t="inlineStr">
         <is>
           <t>Disusun oleh</t>
         </is>
       </c>
-      <c r="B35" s="36" t="inlineStr">
+      <c r="B35" s="28" t="inlineStr">
         <is>
           <t>Erik Dwi Yanto / Technical/Operation Engineer L1</t>
         </is>
       </c>
-      <c r="C35" s="36" t="n"/>
-      <c r="D35" s="36" t="n"/>
+      <c r="C35" s="28" t="n"/>
+      <c r="D35" s="28" t="n"/>
+      <c r="E35" s="44" t="n"/>
     </row>
     <row r="36" ht="27.75" customHeight="1" s="24">
-      <c r="A36" s="36" t="inlineStr">
+      <c r="A36" s="28" t="inlineStr">
         <is>
           <t>Diperiksa oleh</t>
         </is>
       </c>
-      <c r="B36" s="36" t="inlineStr">
+      <c r="B36" s="28" t="inlineStr">
         <is>
           <t>Fani Fatullah / VP Tech Operation and Services</t>
         </is>
       </c>
-      <c r="C36" s="36" t="n"/>
-      <c r="D36" s="36" t="n"/>
+      <c r="C36" s="28" t="n"/>
+      <c r="D36" s="28" t="n"/>
+      <c r="E36" s="44" t="n"/>
     </row>
     <row r="37" ht="27.75" customHeight="1" s="24">
-      <c r="A37" s="36" t="inlineStr">
+      <c r="A37" s="28" t="inlineStr">
         <is>
           <t>Disetujui oleh</t>
         </is>
       </c>
-      <c r="B37" s="36" t="inlineStr">
+      <c r="B37" s="28" t="inlineStr">
         <is>
           <t>Samuel Kristanto Utomo / President Director</t>
         </is>
       </c>
-      <c r="C37" s="36" t="n"/>
-      <c r="D37" s="36" t="n"/>
+      <c r="C37" s="28" t="n"/>
+      <c r="D37" s="28" t="n"/>
+      <c r="E37" s="44" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -1109,139 +1250,145 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="21" customWidth="1" style="23" min="1" max="1"/>
     <col width="16" customWidth="1" style="23" min="2" max="5"/>
+    <col width="13" customWidth="1" style="24" min="3" max="3"/>
+    <col width="13" customWidth="1" style="24" min="4" max="4"/>
+    <col width="14" customWidth="1" style="24" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="24">
-      <c r="A1" s="38" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="24">
+      <c r="A1" s="50" t="inlineStr">
         <is>
           <t>Status personel</t>
         </is>
       </c>
-      <c r="B1" s="38" t="inlineStr">
+      <c r="B1" s="50" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="C1" s="38" t="inlineStr">
+      <c r="C1" s="50" t="inlineStr">
         <is>
           <t>MFA</t>
         </is>
       </c>
-      <c r="D1" s="38" t="inlineStr">
+      <c r="D1" s="50" t="inlineStr">
         <is>
           <t>Status akun</t>
         </is>
       </c>
-      <c r="E1" s="38" t="inlineStr">
+      <c r="E1" s="50" t="inlineStr">
         <is>
           <t>Keputusan</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="24">
-      <c r="A2" s="30" t="inlineStr">
+    <row r="2" ht="16.5" customHeight="1" s="24">
+      <c r="A2" s="51" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="B2" s="30" t="inlineStr">
+      <c r="B2" s="51" t="inlineStr">
         <is>
           <t>Read-only</t>
         </is>
       </c>
-      <c r="C2" s="30" t="inlineStr">
+      <c r="C2" s="51" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="D2" s="30" t="inlineStr">
+      <c r="D2" s="51" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="E2" s="30" t="inlineStr">
+      <c r="E2" s="51" t="inlineStr">
         <is>
           <t>Tetap</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="24">
-      <c r="A3" s="30" t="inlineStr">
+    <row r="3" ht="16.5" customHeight="1" s="24">
+      <c r="A3" s="51" t="inlineStr">
         <is>
           <t>Mutasi</t>
         </is>
       </c>
-      <c r="B3" s="30" t="inlineStr">
+      <c r="B3" s="51" t="inlineStr">
         <is>
           <t>Operator</t>
         </is>
       </c>
-      <c r="C3" s="30" t="inlineStr">
+      <c r="C3" s="51" t="inlineStr">
         <is>
           <t>Tidak</t>
         </is>
       </c>
-      <c r="D3" s="30" t="inlineStr">
+      <c r="D3" s="51" t="inlineStr">
         <is>
           <t>Dinonaktifkan</t>
         </is>
       </c>
-      <c r="E3" s="30" t="inlineStr">
+      <c r="E3" s="51" t="inlineStr">
         <is>
           <t>Ubah</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="24">
-      <c r="A4" s="30" t="inlineStr">
+    <row r="4" ht="30" customHeight="1" s="24">
+      <c r="A4" s="51" t="inlineStr">
         <is>
           <t>Keluar</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="C4" s="30" t="inlineStr">
+      <c r="C4" s="51" t="inlineStr">
         <is>
           <t>Tidak didukung</t>
         </is>
       </c>
-      <c r="D4" s="30" t="inlineStr">
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Dicabut</t>
         </is>
       </c>
-      <c r="E4" s="30" t="inlineStr">
+      <c r="E4" s="51" t="inlineStr">
         <is>
           <t>Cabut</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="24">
-      <c r="A5" s="30" t="inlineStr">
+    <row r="5" ht="30" customHeight="1" s="24">
+      <c r="A5" s="51" t="inlineStr">
         <is>
           <t>Vendor atau partner</t>
         </is>
       </c>
-      <c r="B5" s="30" t="inlineStr">
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Privileged</t>
         </is>
       </c>
+      <c r="C5" s="52" t="n"/>
+      <c r="D5" s="52" t="n"/>
+      <c r="E5" s="52" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -1261,10 +1408,16 @@
     <col width="22" customWidth="1" style="23" min="5" max="5"/>
     <col width="14" customWidth="1" style="23" min="6" max="6"/>
     <col width="10" customWidth="1" style="23" min="7" max="7"/>
-    <col width="9" customWidth="1" style="23" min="8" max="9"/>
+    <col width="15" customWidth="1" style="23" min="8" max="9"/>
+    <col width="13" customWidth="1" style="24" min="9" max="9"/>
     <col width="11" customWidth="1" style="23" min="10" max="10"/>
     <col width="15" customWidth="1" style="23" min="11" max="11"/>
-    <col width="11" customWidth="1" style="23" min="12" max="17"/>
+    <col width="14" customWidth="1" style="23" min="12" max="17"/>
+    <col width="13" customWidth="1" style="24" min="13" max="13"/>
+    <col width="13" customWidth="1" style="24" min="14" max="14"/>
+    <col width="13" customWidth="1" style="24" min="15" max="15"/>
+    <col width="13" customWidth="1" style="24" min="16" max="16"/>
+    <col width="15" customWidth="1" style="24" min="17" max="17"/>
     <col width="9" customWidth="1" style="23" min="18" max="18"/>
     <col width="16" customWidth="1" style="23" min="19" max="19"/>
   </cols>
@@ -1279,7 +1432,7 @@
     <row r="2" ht="15" customHeight="1" s="24">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>Kolom abu-abu dihitung otomatis.</t>
+          <t>Kolom abu-abu terisi otomatis.</t>
         </is>
       </c>
     </row>
@@ -8981,7 +9134,7 @@
   </dataValidations>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="8" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -9000,9 +9153,10 @@
     <col width="18" customWidth="1" style="23" min="4" max="4"/>
     <col width="10" customWidth="1" style="23" min="5" max="5"/>
     <col width="18" customWidth="1" style="23" min="6" max="6"/>
-    <col width="9" customWidth="1" style="23" min="7" max="7"/>
+    <col width="14" customWidth="1" style="23" min="7" max="7"/>
     <col width="26" customWidth="1" style="23" min="8" max="8"/>
     <col width="11" customWidth="1" style="23" min="9" max="10"/>
+    <col width="13" customWidth="1" style="24" min="10" max="10"/>
     <col width="16" customWidth="1" style="23" min="11" max="11"/>
     <col width="10" customWidth="1" style="23" min="12" max="12"/>
   </cols>
@@ -9017,11 +9171,11 @@
     <row r="2" ht="15" customHeight="1" s="24">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>Satu baris per akun yang ditinjau. Setelah review, perbarui kolom Review terakhir di Register Akses.</t>
+          <t>Isi satu baris untuk setiap akun yang ditinjau. Setelah review selesai, perbarui kolom Review terakhir di Register Akses.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="31.5" customHeight="1" s="24">
+    <row r="4" ht="43.5" customHeight="1" s="24">
       <c r="A4" s="39" t="inlineStr">
         <is>
           <t>Periode review</t>
@@ -12526,7 +12680,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
@@ -12622,6 +12776,6 @@
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>